--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92547984901</v>
+        <v>46157.93098456125</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93098456125</v>
+        <v>46157.9312517491</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9312517491</v>
+        <v>46157.93374742151</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93374742151</v>
+        <v>46157.93683666299</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93683666299</v>
+        <v>46158.28199910513</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28199910513</v>
+        <v>46158.29727890333</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29727890333</v>
+        <v>46158.29796484633</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29796484633</v>
+        <v>46158.33362332436</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33362332436</v>
+        <v>46158.37213784159</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37213784159</v>
+        <v>46158.37270500837</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
